--- a/survey_templates/036_investor_business_venture_interest_poll--survey_templates.xlsx
+++ b/survey_templates/036_investor_business_venture_interest_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>What is the primary factor that investors consider when evaluating a business venture?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>what_do_investors_see</t>
+          <t>investor_success_measures</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_do_investors_see</t>
+          <t>How do investors measure the success of their investments?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what_do_investors_seek</t>
+          <t>investment_criteria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what_do_investors_seek</t>
+          <t>What do investors look for when considering an investment opportunity?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>how_do_investors_prioritise</t>
+          <t>research_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_do_investors_prioritise</t>
+          <t>How often do investors conduct research on a company before investing?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>what_do_investors_prefer</t>
+          <t>expected_return_on_investment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_do_investors_prefer</t>
+          <t>What is the expected return on investment for most investors?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>why_do_investors_invest</t>
+          <t>industry_trends</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>why_do_investors_invest</t>
+          <t>How do investors view the current state of their industry?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>when_do_investors_invest</t>
+          <t>investment_priorities</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>when_do_investors_invest</t>
+          <t>What are the primary goals that investors prioritize when making investment decisions?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what_do_investors_expect</t>
+          <t>progress_measurement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what_do_investors_expect</t>
+          <t>How do investors measure the progress of their investments?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what_do_investors_look_for</t>
+          <t>investment_return_expectations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>what_do_investors_look_for</t>
+          <t>What do investors expect in terms of return on investment?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_success</t>
+          <t>founder_relationships</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_success</t>
+          <t>How do investors view their fellow founders?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what_do_investors_support</t>
+          <t>value_measurement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_do_investors_support</t>
+          <t>How do investors measure the value of a company?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_progress</t>
+          <t>market_trends</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_progress</t>
+          <t>How often do investors review market trends?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
+          <t>market_trends_view</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
+          <t>How do investors view market trends?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,269 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>how_do_investors_view_competitors</t>
+          <t>value_measures</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>how_do_investors_view_competitors</t>
+          <t>What do investors prioritize when evaluating a company's value?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_success</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_success</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_industry</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_industry</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_fellow_founders</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_fellow_founders</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_founding_team</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_founding_team</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>what_do_investors_support</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>what_do_investors_support</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_value</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_value</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_trends</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_trends</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,1394 +873,714 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>what_do_investors_see_choices</t>
+          <t>introduction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>growth_potential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Growth potential</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>what_do_investors_see_choices</t>
+          <t>introduction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>risk_management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Risk management</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>what_do_investors_see_choices</t>
+          <t>introduction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>financial_returns</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Financial returns</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>what_do_investors_seek_choices</t>
+          <t>investor_success_measures_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>revenue_growth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Revenue growth</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>what_do_investors_seek_choices</t>
+          <t>investor_success_measures_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>market_share</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Market share</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>what_do_investors_seek_choices</t>
+          <t>investor_success_measures_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Customer satisfaction</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>what_do_investors_seek_choices</t>
+          <t>investment_criteria_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>strong_management_team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Strong management team</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_do_investors_prioritise_choices</t>
+          <t>investment_criteria_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>unique_value_proposition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Unique value proposition</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_do_investors_prioritise_choices</t>
+          <t>investment_criteria_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>scalability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Scalability</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_do_investors_prioritise_choices</t>
+          <t>research_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>what_do_investors_prefer_choices</t>
+          <t>research_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>what_do_investors_prefer_choices</t>
+          <t>research_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>what_do_investors_prefer_choices</t>
+          <t>expected_return_on_investment_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>10-20%_annual_returns</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>10-20% annual returns</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>what_do_investors_prefer_choices</t>
+          <t>expected_return_on_investment_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>20-50%_annual_returns</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>20-50% annual returns</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>why_do_investors_invest_choices</t>
+          <t>expected_return_on_investment_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>50%_or_more_annual_returns</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>50% or more annual returns</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>why_do_investors_invest_choices</t>
+          <t>industry_trends_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Bullish</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>why_do_investors_invest_choices</t>
+          <t>industry_trends_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Bearish</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>when_do_investors_invest_choices</t>
+          <t>industry_trends_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>when_do_investors_invest_choices</t>
+          <t>investment_priorities_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>return_on_investment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Return on investment</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>when_do_investors_invest_choices</t>
+          <t>investment_priorities_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>risk_management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Risk management</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_choices</t>
+          <t>investment_priorities_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>social_impact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Social impact</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_choices</t>
+          <t>progress_measurement_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>financial_metrics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Financial metrics</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_choices</t>
+          <t>progress_measurement_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>operational_efficiency</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Operational efficiency</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_choices</t>
+          <t>progress_measurement_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>customer_feedback</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Customer feedback</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>what_do_investors_look_for_choices</t>
+          <t>investment_return_expectations_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>10-20%_annual_returns</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>10-20% annual returns</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>what_do_investors_look_for_choices</t>
+          <t>investment_return_expectations_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>20-50%_annual_returns</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>20-50% annual returns</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>what_do_investors_look_for_choices</t>
+          <t>investment_return_expectations_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>50%_or_more_annual_returns</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>50% or more annual returns</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>what_do_investors_look_for_choices</t>
+          <t>founder_relationships_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_success_choices</t>
+          <t>founder_relationships_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_success_choices</t>
+          <t>founder_relationships_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_success_choices</t>
+          <t>value_measurement_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>financial_metrics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Financial metrics</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>what_do_investors_support_choices</t>
+          <t>value_measurement_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>operational_efficiency</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Operational efficiency</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>what_do_investors_support_choices</t>
+          <t>value_measurement_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Customer satisfaction</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>what_do_investors_support_choices</t>
+          <t>market_trends_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>what_do_investors_support_choices</t>
+          <t>market_trends_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_progress_choices</t>
+          <t>market_trends_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_progress_choices</t>
+          <t>market_trends_view_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>bullish</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Bullish</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>how_do_investors_measure_progress_choices</t>
+          <t>market_trends_view_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>bearish</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Bearish</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
+          <t>market_trends_view_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
+          <t>value_measures_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>financial_metrics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Financial metrics</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
+          <t>value_measures_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>operational_efficiency</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Operational efficiency</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>how_do_investors_view_competitors_choices</t>
+          <t>value_measures_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_competitors_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_competitors_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_competitors_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_success_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_success_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_success_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_industry_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_industry_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_industry_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_industry_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_fellow_founders_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_fellow_founders_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_fellow_founders_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_founding_team_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_founding_team_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_founding_team_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>what_do_investors_support_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>what_do_investors_support_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>what_do_investors_support_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>what_do_investors_support_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_value_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_value_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>how_do_investors_measure_value_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_trends_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_trends_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>how_do_investors_view_market_trends_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>what_do_investors_expect_in_return_on_investment_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Customer satisfaction</t>
         </is>
       </c>
     </row>
